--- a/偏科检测报告.xlsx
+++ b/偏科检测报告.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kin9/python_code/score analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E019FE9B-E651-8240-AF01-08C239897B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAA30B1A-4E52-5149-A8C0-0DB72EFF2D5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4440" yWindow="760" windowWidth="24960" windowHeight="17200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="38">
   <si>
     <t>姓名</t>
   </si>
@@ -40,136 +40,100 @@
     <t>最弱科目</t>
   </si>
   <si>
+    <t>扣分</t>
+  </si>
+  <si>
+    <t>赵六</t>
+  </si>
+  <si>
+    <t>严重偏科</t>
+  </si>
+  <si>
+    <t>数学(96.67%)</t>
+  </si>
+  <si>
+    <t>英语(40.0%)</t>
+  </si>
+  <si>
     <t>孙八</t>
   </si>
   <si>
+    <t>数学(88.0%)</t>
+  </si>
+  <si>
+    <t>物理(45.0%)</t>
+  </si>
+  <si>
+    <t>吴十</t>
+  </si>
+  <si>
+    <t>明显偏科</t>
+  </si>
+  <si>
+    <t>数学(98.67%)</t>
+  </si>
+  <si>
+    <t>化学(48.0%)</t>
+  </si>
+  <si>
+    <t>冯十二</t>
+  </si>
+  <si>
+    <t>物理(85.0%)</t>
+  </si>
+  <si>
+    <t>生物(35.0%)</t>
+  </si>
+  <si>
+    <t>王五</t>
+  </si>
+  <si>
+    <t>物理(95.0%)</t>
+  </si>
+  <si>
+    <t>语文(50.0%)</t>
+  </si>
+  <si>
+    <t>李四</t>
+  </si>
+  <si>
     <t>均衡发展</t>
   </si>
   <si>
-    <t>语文(88.67%)</t>
-  </si>
-  <si>
-    <t>生物(71.0%)</t>
+    <t>生物(72.0%)</t>
+  </si>
+  <si>
+    <t>周九</t>
+  </si>
+  <si>
+    <t>数学(90.0%)</t>
+  </si>
+  <si>
+    <t>语文(66.67%)</t>
   </si>
   <si>
     <t>钱七</t>
   </si>
   <si>
-    <t>物理(90.0%)</t>
-  </si>
-  <si>
-    <t>语文(72.0%)</t>
-  </si>
-  <si>
-    <t>李四</t>
-  </si>
-  <si>
-    <t>英语(98.67%)</t>
-  </si>
-  <si>
-    <t>数学(86.0%)</t>
+    <t>数学(80.0%)</t>
+  </si>
+  <si>
+    <t>张三</t>
+  </si>
+  <si>
+    <t>英语(93.33%)</t>
+  </si>
+  <si>
+    <t>生物(88.0%)</t>
   </si>
   <si>
     <t>郑十一</t>
   </si>
   <si>
-    <t>化学(74.0%)</t>
-  </si>
-  <si>
-    <t>生物(56.0%)</t>
-  </si>
-  <si>
-    <t>陈十三</t>
-  </si>
-  <si>
-    <t>生物(73.0%)</t>
-  </si>
-  <si>
-    <t>英语(56.67%)</t>
-  </si>
-  <si>
-    <t>吴十</t>
-  </si>
-  <si>
-    <t>英语(70.0%)</t>
-  </si>
-  <si>
-    <t>语文(53.33%)</t>
-  </si>
-  <si>
-    <t>张三</t>
-  </si>
-  <si>
-    <t>语文(97.33%)</t>
-  </si>
-  <si>
-    <t>数学(83.33%)</t>
-  </si>
-  <si>
-    <t>赵六</t>
-  </si>
-  <si>
-    <t>数学(99.33%)</t>
-  </si>
-  <si>
-    <t>物理(83.0%)</t>
-  </si>
-  <si>
-    <t>冯十二</t>
-  </si>
-  <si>
-    <t>物理(74.0%)</t>
-  </si>
-  <si>
-    <t>语文(58.67%)</t>
-  </si>
-  <si>
-    <t>周九</t>
-  </si>
-  <si>
-    <t>化学(69.0%)</t>
-  </si>
-  <si>
-    <t>卫十五</t>
-  </si>
-  <si>
-    <t>语文(61.33%)</t>
-  </si>
-  <si>
-    <t>沈十七</t>
-  </si>
-  <si>
-    <t>语文(68.67%)</t>
-  </si>
-  <si>
-    <t>化学(56.0%)</t>
-  </si>
-  <si>
-    <t>楚十四</t>
-  </si>
-  <si>
-    <t>物理(69.0%)</t>
-  </si>
-  <si>
-    <t>数学(56.67%)</t>
-  </si>
-  <si>
-    <t>王五</t>
-  </si>
-  <si>
-    <t>英语(94.0%)</t>
-  </si>
-  <si>
-    <t>化学(82.0%)</t>
-  </si>
-  <si>
-    <t>蒋十六</t>
-  </si>
-  <si>
-    <t>语文(69.33%)</t>
-  </si>
-  <si>
-    <t>英语(58.67%)</t>
+    <t>英语(73.33%)</t>
+  </si>
+  <si>
+    <t>生物(68.0%)</t>
   </si>
 </sst>
 </file>
@@ -541,15 +505,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="3" width="23" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="6" width="23" customWidth="1"/>
+    <col min="1" max="7" width="11.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -568,305 +530,238 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2">
-        <v>7.82</v>
+        <v>22.16</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2">
-        <v>79.94</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2">
+        <v>-60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3">
+        <v>20.58</v>
+      </c>
+      <c r="C3" t="s">
         <v>8</v>
       </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3">
-        <v>6.95</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
       <c r="D3">
-        <v>79.56</v>
+        <v>73</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>13</v>
+      </c>
+      <c r="G3">
+        <v>-60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4">
-        <v>6.7</v>
+        <v>19.68</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D4">
-        <v>92.11</v>
+        <v>58.67</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5">
+        <v>19.059999999999999</v>
+      </c>
+      <c r="C5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
+      <c r="D5">
+        <v>73.67</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6">
+        <v>17.46</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6">
+        <v>85.28</v>
+      </c>
+      <c r="E6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7">
+        <v>9.5299999999999994</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7">
+        <v>79.83</v>
+      </c>
+      <c r="E7" t="s">
         <v>16</v>
       </c>
-      <c r="B5">
-        <v>6.44</v>
-      </c>
-      <c r="C5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5">
-        <v>63.89</v>
-      </c>
-      <c r="E5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6">
-        <v>6.2</v>
-      </c>
-      <c r="C6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6">
-        <v>66.17</v>
-      </c>
-      <c r="E6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7">
-        <v>6.12</v>
-      </c>
-      <c r="C7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7">
-        <v>65.39</v>
-      </c>
-      <c r="E7" t="s">
-        <v>23</v>
-      </c>
       <c r="F7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>26</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8">
+        <v>8.52</v>
+      </c>
+      <c r="C8" t="s">
         <v>25</v>
       </c>
-      <c r="B8">
-        <v>6.02</v>
-      </c>
-      <c r="C8" t="s">
-        <v>7</v>
-      </c>
       <c r="D8">
-        <v>91.78</v>
+        <v>73.83</v>
       </c>
       <c r="E8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9">
+        <v>2.88</v>
+      </c>
+      <c r="C9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9">
+        <v>76.72</v>
+      </c>
+      <c r="E9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" t="s">
         <v>26</v>
       </c>
-      <c r="F8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9">
-        <v>6.02</v>
-      </c>
-      <c r="C9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9">
-        <v>89.94</v>
-      </c>
-      <c r="E9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="G9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B10">
-        <v>5.64</v>
+        <v>1.92</v>
       </c>
       <c r="C10" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="D10">
-        <v>67.17</v>
+        <v>90.89</v>
       </c>
       <c r="E10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>34</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B11">
-        <v>5.6</v>
+        <v>1.92</v>
       </c>
       <c r="C11" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="D11">
-        <v>76.56</v>
+        <v>70.89</v>
       </c>
       <c r="E11" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" t="s">
-        <v>36</v>
-      </c>
-      <c r="B12">
-        <v>5.31</v>
-      </c>
-      <c r="C12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12">
-        <v>68.06</v>
-      </c>
-      <c r="E12" t="s">
-        <v>17</v>
-      </c>
-      <c r="F12" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13">
-        <v>4.79</v>
-      </c>
-      <c r="C13" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13">
-        <v>64</v>
-      </c>
-      <c r="E13" t="s">
-        <v>39</v>
-      </c>
-      <c r="F13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" t="s">
-        <v>41</v>
-      </c>
-      <c r="B14">
-        <v>4.68</v>
-      </c>
-      <c r="C14" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14">
-        <v>64</v>
-      </c>
-      <c r="E14" t="s">
-        <v>42</v>
-      </c>
-      <c r="F14" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" t="s">
-        <v>44</v>
-      </c>
-      <c r="B15">
-        <v>4.2300000000000004</v>
-      </c>
-      <c r="C15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15">
-        <v>89.33</v>
-      </c>
-      <c r="E15" t="s">
-        <v>45</v>
-      </c>
-      <c r="F15" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" t="s">
-        <v>47</v>
-      </c>
-      <c r="B16">
-        <v>3.58</v>
-      </c>
-      <c r="C16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16">
-        <v>62.89</v>
-      </c>
-      <c r="E16" t="s">
-        <v>48</v>
-      </c>
-      <c r="F16" t="s">
-        <v>49</v>
+      <c r="G11">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
